--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:19</t>
+    <t xml:space="preserve">2026-09-09 22:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:18</t>
+    <t xml:space="preserve">2026-09-17 13:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="3">
@@ -1115,26 +1115,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.86</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.03</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="7">
@@ -1175,35 +1175,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.56</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="5">
@@ -1241,101 +1241,101 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.76</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4.37</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6.81</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4.86</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6.04</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3.9</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3.03</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3.69</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="17">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:44</t>
+    <t xml:space="preserve">2026-09-25 21:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -536,7 +536,7 @@
         <v>-1.16</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-23.87</v>
+        <v>-23.91</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>7</v>
@@ -556,10 +556,10 @@
         <v>3.15</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-27.62</v>
+        <v>-27.46</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>7</v>
@@ -582,7 +582,7 @@
         <v>-0.98</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-25.26</v>
+        <v>-25.31</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>7</v>
@@ -605,7 +605,7 @@
         <v>-1.01</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-21.35</v>
+        <v>-21.26</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>6</v>
@@ -625,10 +625,10 @@
         <v>3.2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.77</v>
+        <v>-0.78</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-24.06</v>
+        <v>-24.27</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>6</v>
@@ -648,10 +648,10 @@
         <v>3.9</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.88</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-22.31</v>
+        <v>-22.49</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>6</v>
@@ -674,7 +674,7 @@
         <v>-1.05</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-21.6</v>
+        <v>-21.54</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>5</v>
@@ -697,7 +697,7 @@
         <v>-0.87</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-25.22</v>
+        <v>-25.19</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>5</v>
@@ -720,7 +720,7 @@
         <v>-0.94</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-23.04</v>
+        <v>-23.12</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5</v>
@@ -743,7 +743,7 @@
         <v>-0.95</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-19.55</v>
+        <v>-19.45</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         <v>-0.8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-23.67</v>
+        <v>-23.75</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>4</v>
@@ -789,7 +789,7 @@
         <v>-0.86</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-21.34</v>
+        <v>-21.32</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>4</v>
@@ -812,7 +812,7 @@
         <v>-1.18</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-22.35</v>
+        <v>-22.33</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>3</v>
@@ -835,7 +835,7 @@
         <v>-1.16</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-26.48</v>
+        <v>-26.53</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>3</v>
@@ -858,7 +858,7 @@
         <v>-1.17</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-24.58</v>
+        <v>-24.48</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>3</v>
@@ -878,10 +878,10 @@
         <v>5.59</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-1.37</v>
+        <v>-1.36</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-24.51</v>
+        <v>-24.4</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>2</v>
@@ -904,7 +904,7 @@
         <v>-1.34</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-29.13</v>
+        <v>-29.04</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2</v>
@@ -924,10 +924,10 @@
         <v>5.01</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-1.35</v>
+        <v>-1.34</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-26.95</v>
+        <v>-26.85</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>2</v>
@@ -947,10 +947,10 @@
         <v>7.01</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-1.76</v>
+        <v>-1.77</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-25.11</v>
+        <v>-25.22</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1</v>
@@ -973,7 +973,7 @@
         <v>-2.08</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-31.18</v>
+        <v>-31.2</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>-1.95</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-28.63</v>
+        <v>-28.62</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_metropolitana.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:42</t>
+    <t xml:space="preserve">2026-10-05 07:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
